--- a/Pruebas calificadas/COLEGIO JORGE SOTO DEL CORRAL CURSO 902_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO JORGE SOTO DEL CORRAL CURSO 902_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1309,11 +1301,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -1321,7 +1309,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1562,11 +1550,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -1574,7 +1558,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1815,11 +1799,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -1827,7 +1807,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2064,11 +2044,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -2076,7 +2052,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2317,11 +2293,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -2329,7 +2301,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2570,11 +2542,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -2582,7 +2550,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2823,11 +2791,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -2835,7 +2799,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3076,11 +3040,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -3088,7 +3048,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3261,11 +3221,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -3273,7 +3229,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3514,11 +3470,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -3526,7 +3478,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3767,11 +3719,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -3779,7 +3727,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4020,11 +3968,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -4032,7 +3976,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4273,11 +4217,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -4285,7 +4225,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4526,11 +4466,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -4538,7 +4474,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4779,11 +4715,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -4791,7 +4723,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5032,11 +4964,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -5044,7 +4972,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5285,11 +5213,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -5297,7 +5221,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5538,11 +5462,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -5550,7 +5470,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5791,11 +5711,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -5803,7 +5719,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6044,11 +5960,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -6056,7 +5968,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6297,11 +6209,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -6309,7 +6217,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6550,11 +6458,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -6562,7 +6466,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6803,11 +6707,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -6815,7 +6715,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7056,11 +6956,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -7068,7 +6964,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7309,11 +7205,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -7321,7 +7213,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7562,11 +7454,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -7574,7 +7462,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7815,11 +7703,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -7827,7 +7711,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8068,11 +7952,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -8080,7 +7960,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8321,11 +8201,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -8333,7 +8209,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8574,11 +8450,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -8586,7 +8458,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8827,11 +8699,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -8839,7 +8707,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9080,11 +8948,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001032409</t>
@@ -9092,7 +8956,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE SOTO DEL CORRAL (IED)</t>
+          <t>COLEGIO JORGE SOTO DEL CORRAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
